--- a/Rastreador GPS+Maps/Resources/Modelo_reporte_P.xlsx
+++ b/Rastreador GPS+Maps/Resources/Modelo_reporte_P.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Indice</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Reporte de mediciones de Radiaciones No Ionizantes</t>
+  </si>
+  <si>
+    <t>“2025, Año de la Reconstrucción de la Nación Argentina”</t>
   </si>
 </sst>
 </file>
@@ -71,11 +74,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,11 +139,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -164,37 +166,31 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>15241</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>813556</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>119413</xdr:rowOff>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>92093</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="2 Imagen"/>
+        <xdr:cNvPr id="4" name="3 Imagen"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="15241"/>
-          <a:ext cx="2459476" cy="538512"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1738313" cy="1151749"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -505,20 +501,22 @@
     <col min="9" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.9" x14ac:dyDescent="0.2">
-      <c r="H1" s="6"/>
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" ht="10.9" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:8" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
